--- a/BASE DE DATOS DE CURSOS DE CAPACITACION VSA.xlsx
+++ b/BASE DE DATOS DE CURSOS DE CAPACITACION VSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csanchez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9712256D-E731-4C66-B158-AA35790907DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D41CDD-E781-4402-B90E-9ED29C22B2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3A8DC8B-C958-42F5-AF9D-D94772EB178A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="32">
   <si>
     <t>nomina</t>
   </si>
@@ -71,9 +71,6 @@
     <t>pedro</t>
   </si>
   <si>
-    <t>basico de seguridad</t>
-  </si>
-  <si>
     <t>anexo sspa</t>
   </si>
   <si>
@@ -86,18 +83,9 @@
     <t>tipo de curso</t>
   </si>
   <si>
-    <t>seguridad</t>
-  </si>
-  <si>
     <t>comunicación efectiva</t>
   </si>
   <si>
-    <t>habilidades</t>
-  </si>
-  <si>
-    <t>técnicos</t>
-  </si>
-  <si>
     <t>trabajo en equipo</t>
   </si>
   <si>
@@ -111,6 +99,42 @@
   </si>
   <si>
     <t>llenado rápido</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>Técnicos</t>
+  </si>
+  <si>
+    <t>Complementarios</t>
+  </si>
+  <si>
+    <t>Anexo sspa</t>
+  </si>
+  <si>
+    <t>Basico de seguridad</t>
+  </si>
+  <si>
+    <t>Comunicación efectiva</t>
+  </si>
+  <si>
+    <t>Llenado rápido</t>
+  </si>
+  <si>
+    <t>Alineación</t>
+  </si>
+  <si>
+    <t>Uso y manejo de herramientas</t>
+  </si>
+  <si>
+    <t>Supervision</t>
+  </si>
+  <si>
+    <t>Trabajo en equipo</t>
+  </si>
+  <si>
+    <t>Alineación de Tuberias</t>
   </si>
 </sst>
 </file>
@@ -522,9 +546,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -540,7 +564,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -560,7 +584,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -571,19 +595,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F3" s="3">
         <v>46492</v>
@@ -591,19 +615,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5">
         <v>46032</v>
@@ -617,10 +641,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>7</v>
@@ -637,10 +661,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -657,10 +681,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>7</v>
@@ -677,10 +701,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>7</v>
@@ -697,10 +721,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>7</v>
@@ -717,10 +741,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -737,10 +761,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>7</v>
@@ -751,16 +775,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>7</v>
@@ -771,16 +795,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>7</v>
@@ -791,16 +815,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>1679</v>
+        <v>1675</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -811,16 +835,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>7</v>
@@ -831,16 +855,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>1681</v>
+        <v>1675</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>7</v>
@@ -851,16 +875,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>1682</v>
+        <v>1675</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>7</v>
@@ -871,16 +895,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -891,16 +915,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>7</v>
@@ -911,16 +935,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>7</v>
@@ -931,16 +955,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>7</v>
